--- a/output/pdf_financials_xlsx/JES.P.xlsx
+++ b/output/pdf_financials_xlsx/JES.P.xlsx
@@ -799,22 +799,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.008755000000000001</v>
+        <v>-0.008755000000000001</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.113093</v>
+        <v>-0.113093</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.078343</v>
+        <v>-0.078343</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.167204</v>
+        <v>-0.167204</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.03916</v>
+        <v>-0.03916</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.027057</v>
+        <v>-0.027057</v>
       </c>
     </row>
     <row r="17">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.008755000000000001</v>
+        <v>-0.008755000000000001</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.113093</v>
+        <v>-0.113093</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.078343</v>
+        <v>-0.078343</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.167204</v>
+        <v>-0.167204</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.03916</v>
+        <v>-0.03916</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.027057</v>
+        <v>-0.027057</v>
       </c>
     </row>
     <row r="21">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.008755000000000001</v>
+        <v>-0.008755000000000001</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.113093</v>
+        <v>-0.113093</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.078343</v>
+        <v>-0.078343</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.167204</v>
+        <v>-0.167204</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.03916</v>
+        <v>-0.03916</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.027057</v>
+        <v>-0.027057</v>
       </c>
     </row>
     <row r="24">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2.827325</v>
+        <v>-2.827325</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.91715</v>
+        <v>-3.91715</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>4.1801</v>
+        <v>-4.1801</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1108,22 +1108,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.008755000000000001</v>
+        <v>-0.008755000000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.113093</v>
+        <v>-0.113093</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.078343</v>
+        <v>-0.078343</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.167204</v>
+        <v>-0.167204</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.03916</v>
+        <v>-0.03916</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.027057</v>
+        <v>-0.027057</v>
       </c>
     </row>
     <row r="28">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.008755000000000001</v>
+        <v>-0.008755000000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.113093</v>
+        <v>-0.113093</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.078343</v>
+        <v>-0.078343</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.167204</v>
+        <v>-0.167204</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.03916</v>
+        <v>-0.03916</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.027057</v>
+        <v>-0.027057</v>
       </c>
     </row>
     <row r="30">
@@ -1220,22 +1220,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2834,19 +2834,19 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.10246</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.10246</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.08495999999999999</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.08495999999999999</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.08495999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -4172,7 +4172,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -5738,22 +5742,22 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.008755000000000001</v>
+        <v>-0.008755000000000001</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.113093</v>
+        <v>-0.113093</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.078343</v>
+        <v>-0.078343</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0.167204</v>
+        <v>-0.167204</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.03916</v>
+        <v>-0.03916</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0.027057</v>
+        <v>-0.027057</v>
       </c>
     </row>
     <row r="41">

--- a/output/pdf_financials_xlsx/JES.P.xlsx
+++ b/output/pdf_financials_xlsx/JES.P.xlsx
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.008755000000000001</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.113093</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.078343</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.167204</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.03916</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.027057</v>
       </c>
     </row>
     <row r="11">
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.008755000000000001</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.113093</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.078343</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.167204</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-0.03916</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-0.027057</v>
       </c>
     </row>
     <row r="12">
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.26125</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.511942</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.492879</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.301785</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.26522</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.234708</v>
       </c>
     </row>
     <row r="35">
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.26125</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.511942</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.492879</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.301785</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.26522</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.234708</v>
       </c>
     </row>
     <row r="37">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.307</v>
+        <v>0.04575</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.511942</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
